--- a/src/ae/experiments/overview_experiencias_cvae.xlsx
+++ b/src/ae/experiments/overview_experiencias_cvae.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -745,6 +745,191 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>run_cvae_20260601_184438</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20260601_184438</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ConditionalVAE_1</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>128</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>mse</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>68</v>
+      </c>
+      <c r="G9" t="n">
+        <v>861.2018616495253</v>
+      </c>
+      <c r="H9" t="n">
+        <v>968.2865507108671</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>run_cvae_20260601_185146</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20260601_185146</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ConditionalVAE_2</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>128</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>l1</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2137.477098991298</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2222.076635228979</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>run_cvae_20260601_185838</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20260601_185838</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ConditionalVAE_beta4</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>128</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>mse</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>48</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1115.306714794304</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1158.280597003253</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>run_cvae_20260601_190500</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20260601_190500</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ConditionalVAE_beta4</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>128</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>mse</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>44</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1412.412874554984</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1441.23658033033</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>run_cvae_20260601_190504</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>20260601_190504</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ConditionalAE</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>128</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>mse</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>36</v>
+      </c>
+      <c r="G13" t="n">
+        <v>539.1621103021163</v>
+      </c>
+      <c r="H13" t="n">
+        <v>589.6656759298361</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
